--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/combined_dry_weight_DB.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/combined_dry_weight_DB.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ooffice KST\New folder\All_random\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ooffice KST\New folder\DB file folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,30 +15,19 @@
     <sheet name="combined dry weight (2)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'combined dry weight (2)'!$A$1:$L$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'combined dry weight (2)'!$A$1:$N$97</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="167">
   <si>
     <t>Sr</t>
   </si>
@@ -536,13 +525,16 @@
   </si>
   <si>
     <t>ROXX 100-100gm</t>
+  </si>
+  <si>
+    <t>COMFO 40-Regular</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -577,8 +569,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,6 +593,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,7 +632,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -696,6 +701,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -983,7 +1000,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
@@ -3848,8 +3865,8 @@
       <c r="G66" s="7">
         <v>1500</v>
       </c>
-      <c r="H66" s="7" t="s">
-        <v>64</v>
+      <c r="H66" s="37" t="s">
+        <v>55</v>
       </c>
       <c r="I66" s="8" t="s">
         <v>15</v>
@@ -5157,8 +5174,48 @@
       </c>
       <c r="N96" s="27"/>
     </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="19">
+        <v>96</v>
+      </c>
+      <c r="B97" s="33">
+        <v>2327</v>
+      </c>
+      <c r="C97" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="D97" s="33">
+        <v>70</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F97" s="33">
+        <v>40</v>
+      </c>
+      <c r="G97" s="33">
+        <v>1500</v>
+      </c>
+      <c r="H97" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I97" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" s="36">
+        <v>112</v>
+      </c>
+      <c r="K97" s="33"/>
+      <c r="L97" s="36">
+        <v>8.9285714285714288</v>
+      </c>
+      <c r="M97" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="N97" s="32"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L96"/>
+  <autoFilter ref="A1:N97"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
